--- a/hamiltonian_core_matrix.xlsx
+++ b/hamiltonian_core_matrix.xlsx
@@ -418,4643 +418,4643 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-2.625758156223651</v>
+        <v>-2808.419024807049</v>
       </c>
       <c r="B1" t="n">
-        <v>-4.610458877449537</v>
+        <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>-5.311296444477563</v>
+        <v>0</v>
       </c>
       <c r="D1" t="n">
-        <v>-5.524769082326569</v>
+        <v>0</v>
       </c>
       <c r="E1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G1" t="n">
-        <v>1.18424814625074e-16</v>
+        <v>0</v>
       </c>
       <c r="H1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J1" t="n">
-        <v>1.108829608974413e-20</v>
+        <v>0</v>
       </c>
       <c r="K1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M1" t="n">
-        <v>1.266644902167352e-16</v>
+        <v>0</v>
       </c>
       <c r="N1" t="n">
-        <v>-9.225808838285239e-08</v>
+        <v>0</v>
       </c>
       <c r="O1" t="n">
-        <v>-0.0447830217635652</v>
+        <v>0</v>
       </c>
       <c r="P1" t="n">
-        <v>-1.311756829374011</v>
+        <v>0</v>
       </c>
       <c r="Q1" t="n">
-        <v>-3.525299693406195</v>
+        <v>0</v>
       </c>
       <c r="R1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T1" t="n">
-        <v>0.02891013421256687</v>
+        <v>0</v>
       </c>
       <c r="U1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W1" t="n">
-        <v>1.460963723260676</v>
+        <v>0</v>
       </c>
       <c r="X1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z1" t="n">
-        <v>4.030962427065225</v>
+        <v>0</v>
       </c>
       <c r="AA1" t="n">
-        <v>-0.04552474968185554</v>
+        <v>0</v>
       </c>
       <c r="AB1" t="n">
-        <v>-1.942726522529708</v>
+        <v>0</v>
       </c>
       <c r="AC1" t="n">
-        <v>-2.990681576991055</v>
+        <v>0</v>
       </c>
       <c r="AD1" t="n">
-        <v>-3.61613763598883</v>
+        <v>0</v>
       </c>
       <c r="AE1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG1" t="n">
-        <v>0.8806956288790436</v>
+        <v>0</v>
       </c>
       <c r="AH1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ1" t="n">
-        <v>1.976756168354736</v>
+        <v>0</v>
       </c>
       <c r="AK1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM1" t="n">
-        <v>2.433228562237852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-4.610458877449537</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-128.0992851482523</v>
+        <v>-2808.419024807045</v>
       </c>
       <c r="C2" t="n">
-        <v>-590.9726924332915</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-750.0433346989255</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.02455888585822e-16</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.171780281059178e-13</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.95852335381931e-15</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2056695418185064</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-22.22284778158778</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-188.5674014973663</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-493.1928022498074</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>15.01928157953148</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>306.4997749728942</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>939.6383536627137</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-15.89217913912899</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-280.3713410114233</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-514.3655671823324</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-699.8700086335487</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>140.5967622368904</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>475.910992149432</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>725.6531451023966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-5.311296444477563</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>-590.9726924332915</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-793.1597952967445</v>
+        <v>-2774.528233268392</v>
       </c>
       <c r="D3" t="n">
-        <v>-19054.33202041098</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>4.759902490260511e-13</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-31.00297834654811</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-970.4208375728603</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-4900.591478897454</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-13475.73751335548</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>312.183698190647</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5564.169032086529</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>23306.87838142875</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-210.0471579360228</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4683.118613798188</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-11876.6863790952</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-21460.54893211465</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1240.111927499835</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8374.792059049174</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>21156.62088816152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-5.524769082326569</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>-750.0433346989255</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-19054.33202041098</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-4530.387216258242</v>
+        <v>-555.030887280054</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.305851321043822e-13</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-460.5437560620937</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-14029.26759864238</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-74486.45667804479</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-254895.4940765033</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1677.72637299249</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>41032.66412087551</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>294544.7093008936</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1582.061874009036</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-44830.8222710332</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-161354.1444812012</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-464212.5647561616</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>4781.920060452067</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>62323.39757856841</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>353874.9042370653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-7.361880555713465</v>
+        <v>-555.0308872800529</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.3269290583079419</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.834959887770218</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-20.86417781340436</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-5.566130967526725</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-18.44892249849979</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-27.89040285873</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.361880555713465</v>
+        <v>-485.6056516142546</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3269290583079419</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-6.834959887770219</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-20.86417781340436</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-5.566130967526725</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-18.44892249849979</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-27.89040285873</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.18424814625074e-16</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>-4.02455888585822e-16</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>4.759902490260511e-13</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2.305851321043822e-13</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-7.361880555713465</v>
+        <v>-416.2016062272453</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06580088393909854</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.168620937620488</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-15.32476321365818</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-14.64005327938461</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.482395538550214</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>8.919263073600247</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>-3.323457198467862</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-1.906136204076412</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-14.37527048742315</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-11.07011814896216</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-4.344679996727591</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.08065051625261885</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-11.24714573403128</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-24.73697439452295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-336.5013137028571</v>
+        <v>-416.2016062272453</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-108.3450649255027</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-1931.075384563266</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-8088.779991018589</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-856.0468076902456</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-5781.102373293332</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-14604.37350146029</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-336.5013137028571</v>
+        <v>-412.5316766388101</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-108.3450649255027</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1931.075384563266</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-8088.779991018589</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>-856.0468076902454</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>-5781.102373293331</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-14604.37350146029</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.108829608974413e-20</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1.171780281059178e-13</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-336.5013137028572</v>
+        <v>-156.5590962155348</v>
       </c>
       <c r="K10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-30.92005154555179</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-791.0292871119796</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-2539.820496816416</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3329.43390722746</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>141.3846098096289</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>875.3165749597354</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-2484.814470981495</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-99.92245916129251</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1577.753778289817</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2327.867311263307</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1526.694885039122</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>-435.9228059714622</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-4165.649154201183</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-13123.16857411551</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-6141.547511369191</v>
+        <v>-66.82533526852976</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-5795.858742014643</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-141751.0798432155</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1017531.556871692</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-33045.63066133966</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-430688.0817548637</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-2445465.260376914</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-6141.547511369191</v>
+        <v>-66.82533526852974</v>
       </c>
       <c r="M12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-5795.858742014643</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-141751.0798432155</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1017531.556871692</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-33045.63066133967</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-430688.0817548637</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-2445465.260376915</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1.266644902167352e-16</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>-2.95852335381931e-15</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-6141.54751136919</v>
+        <v>-64.09054076946363</v>
       </c>
       <c r="N13" t="n">
-        <v>-1428.147178771161</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-40596.31162835484</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-178094.3976799238</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-400087.836646103</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-923.2229819799672</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-43544.90230452179</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-554745.1804025184</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-2429.877253537517</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-60761.13691661785</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-168852.8714608497</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>-248902.2667717757</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>-26524.31686893059</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-365430.7434336761</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-2255614.808607568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-9.225808838285239e-08</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.2056695418185064</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>-31.00297834654811</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-460.5437560620937</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.06580088393909854</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-30.92005154555179</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-1428.147178771161</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.625758156223651</v>
+        <v>-59.02535540349962</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.610458877449537</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.311296444477563</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.524769082326569</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.18424814625074e-16</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.108829608974413e-20</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.266644902167352e-16</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.04552474968185554</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.942726522529708</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-2.990681576991055</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>-3.61613763598883</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.8806956288790436</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-1.976756168354736</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-2.433228562237852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.0447830217635652</v>
+        <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>-22.22284778158778</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-970.4208375728603</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-14029.26759864238</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.168620937620488</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-791.0292871119796</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-40596.31162835484</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.610458877449537</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-128.0992851482523</v>
+        <v>-28.16159727442432</v>
       </c>
       <c r="P15" t="n">
-        <v>-590.9726924332915</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-750.0433346989255</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.02455888585822e-16</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.171780281059178e-13</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95852335381931e-15</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-15.89217913912899</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-280.3713410114233</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-514.3655671823324</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>-699.8700086335487</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>-140.5967622368904</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-475.910992149432</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-725.6531451023966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-1.311756829374011</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>-188.5674014973663</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>-4900.591478897454</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-74486.45667804479</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-15.32476321365818</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-2539.820496816416</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-178094.3976799238</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.311296444477563</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-590.9726924332915</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-793.1597952967445</v>
+        <v>-17.95662139729773</v>
       </c>
       <c r="Q16" t="n">
-        <v>-19054.33202041098</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.759902490260511e-13</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-210.0471579360228</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-4683.118613798188</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-11876.6863790952</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>-21460.54893211465</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>-1240.111927499835</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-8374.792059049174</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-21156.62088816152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-3.525299693406195</v>
+        <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>-493.1928022498074</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>-13475.73751335548</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-254895.4940765033</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-14.64005327938461</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-3329.43390722746</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-400087.836646103</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.524769082326569</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-750.0433346989255</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-19054.33202041098</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4530.387216258242</v>
+        <v>-17.95662139729709</v>
       </c>
       <c r="R17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-2.305851321043822e-13</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-1582.061874009036</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-44830.8222710332</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-161354.1444812012</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>-464212.5647561616</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>-4781.920060452067</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-62323.39757856841</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-353874.9042370653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3269290583079419</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-108.3450649255027</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-5795.858742014643</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-7.361880555713465</v>
+        <v>-9.507972103246219</v>
       </c>
       <c r="S18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-5.566130967526725</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-18.44892249849979</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-27.89040285873</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3269290583079419</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-108.3450649255027</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-5795.858742014643</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-7.361880555713465</v>
+        <v>-6.323852495613346</v>
       </c>
       <c r="T19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>-5.566130967526725</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>-18.44892249849979</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>-27.89040285873</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.02891013421256687</v>
+        <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>15.01928157953148</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>312.183698190647</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1677.72637299249</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.482395538550214</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>141.3846098096289</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-923.2229819799672</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.18424814625074e-16</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.02455888585822e-16</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.759902490260511e-13</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.305851321043822e-13</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-7.361880555713465</v>
+        <v>-5.027470949428402</v>
       </c>
       <c r="U20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.906136204076412</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>14.37527048742315</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.07011814896216</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.344679996727591</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.08065051625261885</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-11.24714573403128</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>-24.73697439452295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.834959887770218</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-1931.075384563266</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>-141751.0798432155</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-336.5013137028571</v>
+        <v>-4.77695853862113</v>
       </c>
       <c r="V21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-856.0468076902456</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>-5781.102373293332</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>-14604.37350146029</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.834959887770219</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-1931.075384563266</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-141751.0798432155</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-336.5013137028571</v>
+        <v>-4.776958538621041</v>
       </c>
       <c r="W22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>-856.0468076902454</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>-5781.102373293331</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>-14604.37350146029</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.460963723260676</v>
+        <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>306.4997749728942</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>5564.169032086529</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>41032.66412087551</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>8.919263073600247</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>875.3165749597354</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-43544.90230452179</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.108829608974413e-20</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.171780281059178e-13</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-21.65080592737749</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-336.5013137028572</v>
+        <v>0.5661697686769985</v>
       </c>
       <c r="X23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>99.92245916129251</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1577.753778289817</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2327.867311263307</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1526.694885039122</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>-435.9228059714622</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-4165.649154201183</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>-13123.16857411551</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-20.86417781340436</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-8088.779991018589</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>-1017531.556871692</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-6141.547511369191</v>
+        <v>0.566169768677408</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>-33045.63066133966</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>-430688.0817548637</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>-2445465.260376914</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>-20.86417781340436</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-8088.779991018589</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>-1017531.556871692</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>-6141.547511369191</v>
+        <v>0.6650602861264325</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>-33045.63066133967</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>-430688.0817548637</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>-2445465.260376915</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4.030962427065225</v>
+        <v>0</v>
       </c>
       <c r="B26" t="n">
-        <v>939.6383536627137</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>23306.87838142875</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>294544.7093008936</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.323457198467862</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-2484.814470981495</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-554745.1804025184</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.266644902167352e-16</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.95852335381931e-15</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>-31.7659560099498</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-11437.31832385235</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>-6141.54751136919</v>
+        <v>0.9478815385520341</v>
       </c>
       <c r="AA26" t="n">
-        <v>2429.877253537517</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>60761.13691661785</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>168852.8714608497</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>248902.2667717757</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>-26524.31686893059</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-365430.7434336761</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>-2255614.808607568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.04552474968185554</v>
+        <v>0</v>
       </c>
       <c r="B27" t="n">
-        <v>-15.89217913912899</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-210.0471579360228</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-1582.061874009036</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.906136204076412</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-99.92245916129251</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-2429.877253537517</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.04552474968185554</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>-15.89217913912899</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-210.0471579360228</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1582.061874009036</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.906136204076412</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>99.92245916129251</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2429.877253537517</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>-4.330906673150666</v>
+        <v>1.284165238006862</v>
       </c>
       <c r="AB27" t="n">
-        <v>-8.475753889244221</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.674818785350014</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>-10.15698707896573</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-1.942726522529708</v>
+        <v>0</v>
       </c>
       <c r="B28" t="n">
-        <v>-280.3713410114233</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>-4683.118613798188</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-44830.8222710332</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-14.37527048742315</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-1577.753778289817</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-60761.13691661785</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.942726522529708</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>-280.3713410114233</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>-4683.118613798188</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>-44830.8222710332</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>14.37527048742315</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1577.753778289817</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>60761.13691661785</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>-8.475753889244221</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>-218.500468873095</v>
+        <v>1.284165238006926</v>
       </c>
       <c r="AC28" t="n">
-        <v>-2149.971996335692</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>-2887.237541864863</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-2.990681576991055</v>
+        <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>-514.3655671823324</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>-11876.6863790952</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-161354.1444812012</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-11.07011814896216</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-2327.867311263307</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-168852.8714608497</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>-2.990681576991055</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>-514.3655671823324</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-11876.6863790952</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>-161354.1444812012</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>11.07011814896216</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2327.867311263307</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>168852.8714608497</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>-9.674818785350014</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>-2149.971996335692</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1063.905632077963</v>
+        <v>1.541161854938243</v>
       </c>
       <c r="AD29" t="n">
-        <v>-53976.17860959391</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-3.61613763598883</v>
+        <v>0</v>
       </c>
       <c r="B30" t="n">
-        <v>-699.8700086335487</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>-21460.54893211465</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-464212.5647561616</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-4.344679996727591</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-1526.694885039122</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-248902.2667717757</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>-3.61613763598883</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>-699.8700086335487</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-21460.54893211465</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>-464212.5647561616</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>4.344679996727591</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1526.694885039122</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>248902.2667717757</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>-10.15698707896573</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>-2887.237541864863</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>-53976.17860959391</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>-8043.044505202601</v>
+        <v>2.724611937281866</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>-5.566130967526725</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-856.0468076902456</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-33045.63066133966</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>-5.566130967526725</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>-856.0468076902456</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>-33045.63066133966</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>-27.98697548201268</v>
+        <v>3.249959986581969</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>-171.4768559584175</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>-275.2657030911502</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.566130967526725</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>-856.0468076902454</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>-33045.63066133967</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>-5.566130967526725</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>-856.0468076902454</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>-33045.63066133967</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>-27.98697548201268</v>
+        <v>3.664462994468991</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>-171.4768559584175</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>-275.2657030911502</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.8806956288790436</v>
+        <v>0</v>
       </c>
       <c r="B33" t="n">
-        <v>140.5967622368904</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>1240.111927499835</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>4781.920060452067</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.08065051625261885</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-435.9228059714622</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-26524.31686893059</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.8806956288790436</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>-140.5967622368904</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-1240.111927499835</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>-4781.920060452067</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.08065051625261885</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>-435.9228059714622</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>-26524.31686893059</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>-27.98697548201269</v>
+        <v>11.16549252035082</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-171.4768559584175</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>-275.2657030911502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>-18.44892249849979</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-5781.102373293332</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>-430688.0817548637</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>-18.44892249849979</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>-5781.102373293332</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>-430688.0817548637</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>-171.4768559584175</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>-839.8115467062958</v>
+        <v>11.27769499484176</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-99602.23069681383</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>-18.44892249849979</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>-5781.102373293331</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>-430688.0817548637</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>-18.44892249849979</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>-5781.102373293331</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>-430688.0817548637</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>-171.4768559584175</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>-839.8115467062958</v>
+        <v>11.6579762866647</v>
       </c>
       <c r="AJ35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>-99602.23069681383</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.976756168354736</v>
+        <v>0</v>
       </c>
       <c r="B36" t="n">
-        <v>475.910992149432</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>8374.792059049174</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>62323.39757856841</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-11.24714573403128</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-4165.649154201183</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-365430.7434336761</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>-1.976756168354736</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>-475.910992149432</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-8374.792059049174</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>-62323.39757856841</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>-11.24714573403128</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>-4165.649154201183</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>-365430.7434336761</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>-171.4768559584175</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>-839.8115467062956</v>
+        <v>11.65797628666481</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>-99602.23069681381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>-27.89040285873</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-14604.37350146029</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>-2445465.260376914</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>-27.89040285873</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>-14604.37350146029</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>-2445465.260376914</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-275.2657030911502</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>-99602.23069681383</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>-24455.55076156214</v>
+        <v>27.34326986756605</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>-27.89040285873</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>-14604.37350146029</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>-2445465.260376915</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>-27.89040285873</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>-14604.37350146029</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>-2445465.260376915</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>-275.2657030911502</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>-99602.23069681383</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>-24455.55076156214</v>
+        <v>40.05967303184045</v>
       </c>
       <c r="AM38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2.433228562237852</v>
+        <v>0</v>
       </c>
       <c r="B39" t="n">
-        <v>725.6531451023966</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>21156.62088816152</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>353874.9042370653</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-24.73697439452295</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-13123.16857411551</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2255614.808607568</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>-2.433228562237852</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>-725.6531451023966</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-21156.62088816152</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>-353874.9042370653</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>-24.73697439452295</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>-13123.16857411551</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>-2255614.808607568</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>-275.2657030911502</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>-99602.23069681381</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>-24455.55076156213</v>
+        <v>459.1634949960236</v>
       </c>
     </row>
   </sheetData>

--- a/hamiltonian_core_matrix.xlsx
+++ b/hamiltonian_core_matrix.xlsx
@@ -418,16 +418,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-2808.419024807049</v>
+        <v>4.139159679920277</v>
       </c>
       <c r="B1" t="n">
-        <v>0</v>
+        <v>4.439872370214957</v>
       </c>
       <c r="C1" t="n">
-        <v>0</v>
+        <v>2.301202142182699</v>
       </c>
       <c r="D1" t="n">
-        <v>0</v>
+        <v>2.272781618054275</v>
       </c>
       <c r="E1" t="n">
         <v>0</v>
@@ -436,7 +436,7 @@
         <v>0</v>
       </c>
       <c r="G1" t="n">
-        <v>0</v>
+        <v>0.03612803534483141</v>
       </c>
       <c r="H1" t="n">
         <v>0</v>
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="J1" t="n">
-        <v>0</v>
+        <v>0.03074431601516749</v>
       </c>
       <c r="K1" t="n">
         <v>0</v>
@@ -454,19 +454,19 @@
         <v>0</v>
       </c>
       <c r="M1" t="n">
-        <v>0</v>
+        <v>0.03310305217715067</v>
       </c>
       <c r="N1" t="n">
-        <v>0</v>
+        <v>-1.164331493840184e-07</v>
       </c>
       <c r="O1" t="n">
-        <v>0</v>
+        <v>0.00908727878601103</v>
       </c>
       <c r="P1" t="n">
-        <v>0</v>
+        <v>0.5454495722126946</v>
       </c>
       <c r="Q1" t="n">
-        <v>0</v>
+        <v>1.449521828263224</v>
       </c>
       <c r="R1" t="n">
         <v>0</v>
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="T1" t="n">
-        <v>0</v>
+        <v>-0.004917756917705785</v>
       </c>
       <c r="U1" t="n">
         <v>0</v>
@@ -484,7 +484,7 @@
         <v>0</v>
       </c>
       <c r="W1" t="n">
-        <v>0</v>
+        <v>-0.4570860794626933</v>
       </c>
       <c r="X1" t="n">
         <v>0</v>
@@ -493,19 +493,19 @@
         <v>0</v>
       </c>
       <c r="Z1" t="n">
-        <v>0</v>
+        <v>-1.16868944234641</v>
       </c>
       <c r="AA1" t="n">
-        <v>0</v>
+        <v>0.05955589180169553</v>
       </c>
       <c r="AB1" t="n">
-        <v>0</v>
+        <v>1.418553104775894</v>
       </c>
       <c r="AC1" t="n">
-        <v>0</v>
+        <v>1.831416724125386</v>
       </c>
       <c r="AD1" t="n">
-        <v>0</v>
+        <v>2.138875613550525</v>
       </c>
       <c r="AE1" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="AG1" t="n">
-        <v>0</v>
+        <v>-0.5964506393073215</v>
       </c>
       <c r="AH1" t="n">
         <v>0</v>
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="AJ1" t="n">
-        <v>0</v>
+        <v>-0.773537103112676</v>
       </c>
       <c r="AK1" t="n">
         <v>0</v>
@@ -532,21 +532,21 @@
         <v>0</v>
       </c>
       <c r="AM1" t="n">
-        <v>0</v>
+        <v>-0.8272631971284673</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>4.439872370214957</v>
       </c>
       <c r="B2" t="n">
-        <v>-2808.419024807045</v>
+        <v>16.42792488608161</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>15.60550082657199</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>16.46798512610517</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.5819261365744327</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -564,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.475462685247075</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -573,19 +573,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.723285606951114</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.00908727878601104</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.3020651239926924</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>5.049791993425586</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>11.17828061640937</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-0.1787429074991289</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-3.971360158404172</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -612,19 +612,19 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-9.21881277318213</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.576222444784207</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>11.44831120197395</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>13.67190820985699</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>15.84842555965021</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-3.602246001538805</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-5.530407213910946</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -651,21 +651,21 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-5.139031126558099</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>2.301202142182699</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>15.60550082657199</v>
       </c>
       <c r="C3" t="n">
-        <v>-2774.528233268392</v>
+        <v>25.36028734692464</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>51.91216676124913</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -674,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.475462685247074</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6.912828115024684</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -692,19 +692,19 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>13.76609940898933</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.5454495722126947</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>5.049791993425586</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>18.74092126346848</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>38.39856510910838</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-1.124625794116042</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-10.15530698853429</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -731,19 +731,19 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-23.69877968611681</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.508714021200267</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>24.12121622154257</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>38.5077583072274</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>55.30620345657083</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>-3.031657194942603</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-7.76217934737705</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -770,21 +770,21 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-6.456376566773256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>2.272781618054275</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>16.46798512610517</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>51.91216676124913</v>
       </c>
       <c r="D4" t="n">
-        <v>-555.030887280054</v>
+        <v>39.05462463097899</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2.723285606951114</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>13.76609940898933</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -811,19 +811,19 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>43.12718909070011</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.449521828263224</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>11.17828061640937</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>38.39856510910838</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>95.71472975852407</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -832,7 +832,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-2.088945385966567</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-17.40650157142676</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -850,19 +850,19 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-47.39092645945157</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.512122142873354</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>36.21567214747493</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>78.68980267650088</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>151.1499475879253</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0.5487270400261994</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-3.978407090882079</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-11.56233920550879</v>
       </c>
     </row>
     <row r="5">
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-555.0308872800529</v>
+        <v>1.192134315798659</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.766832501424194</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.382854560945209</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.01064078252761629</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.3758371805596659</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.8333571581880173</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.7651230248262965</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.27280487236772</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.097514897426634</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-485.6056516142546</v>
+        <v>1.192134315798659</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.766832501424194</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.382854560945209</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.01064078252761629</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3758371805596659</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.8333571581880168</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.7651230248262962</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.272804872367719</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.097514897426633</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -1132,16 +1132,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>0.03612803534483141</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.5819261365744327</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.475462685247074</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.723285606951114</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1150,7 +1150,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-416.2016062272453</v>
+        <v>1.477838631755247</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.250101211246582</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1168,19 +1168,19 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.194957394976628</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.004917756917705804</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.178742907499129</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.124625794116042</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.088945385966567</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.2169371577703999</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-1.248713956425855</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1207,19 +1207,19 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0.930653878475391</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.6378678045689179</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.760336696370763</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.520531082126993</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.802640033063934</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0.2074482860328148</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.8149003037378533</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.178655034612895</v>
       </c>
     </row>
     <row r="8">
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.766832501424194</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1272,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-416.2016062272453</v>
+        <v>-13.40329958962834</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>20.18728619194507</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.3758371805596656</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.550080082221125</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>12.8982716519249</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>3.676068662738705</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1350,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>13.81389572988589</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>18.37925462552074</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.766832501424194</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-412.5316766388101</v>
+        <v>-13.40329958962834</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>20.18728619194507</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.3758371805596658</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4.550080082221125</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>12.89827165192491</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>3.676068662738704</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>13.81389572988588</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>18.37925462552075</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -1489,16 +1489,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>0.03074431601516749</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.475462685247075</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>6.912828115024684</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>13.76609940898933</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1507,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3.250101211246582</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-156.5590962155348</v>
+        <v>-7.381924980802701</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1525,19 +1525,19 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>44.03641252598699</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.4570860794626934</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.971360158404171</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10.15530698853429</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>17.40650157142676</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1.248713956425854</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-5.357830832620333</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1564,19 +1564,19 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>0.3636216678918136</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.586326549568464</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>10.86627905110093</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>15.44425040665211</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>23.12502089407928</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>4.911791365184697</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>16.06636222813914</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>28.31024971547307</v>
       </c>
     </row>
     <row r="11">
@@ -1620,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1.382854560945209</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>20.18728619194507</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-66.82533526852976</v>
+        <v>-486.8332616027242</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.8333571581880166</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>12.8982716519249</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>68.09819569804129</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>4.518849650494094</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1707,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>37.24777675403165</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>129.7348004269145</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.382854560945209</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>20.18728619194507</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-66.82533526852974</v>
+        <v>-486.8332616027242</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.8333571581880166</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>12.8982716519249</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>68.09819569804129</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>4.518849650494094</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>37.24777675403165</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>129.7348004269146</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
@@ -1846,16 +1846,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>0.03310305217715067</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2.723285606951114</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>13.76609940898933</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>43.12718909070011</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3.194957394976628</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1873,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>44.03641252598699</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1882,19 +1882,19 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-64.09054076946363</v>
+        <v>-436.8057222575121</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.16868944234641</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>9.218812773182133</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>23.69877968611682</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>47.39092645945158</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0.9306538784753915</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.3636216678918154</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1921,19 +1921,19 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>23.68879886756204</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.877188462822925</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>17.2616970864677</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>34.62715650309303</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>60.6386162974352</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>8.709720073795213</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>42.56472805406715</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -1960,21 +1960,21 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>145.0244454550882</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>-1.164331493840184e-07</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.00908727878601104</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.5454495722126947</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1.449521828263224</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.004917756917705804</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.4570860794626934</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2001,19 +2001,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.16868944234641</v>
       </c>
       <c r="N14" t="n">
-        <v>-59.02535540349962</v>
+        <v>4.139159679920277</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.439872370214957</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.301202142182699</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.272781618054275</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0.03612803534483141</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.03074431601516749</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2040,19 +2040,19 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0.03310305217715067</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>0.05955589180169553</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.418553104775894</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.831416724125386</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.138875613550525</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.5964506393073215</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.773537103112676</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2079,21 +2079,21 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>0.8272631971284673</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>0.00908727878601103</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.3020651239926924</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>5.049791993425586</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>11.17828061640937</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.178742907499129</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>3.971360158404171</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2120,19 +2120,19 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>9.218812773182133</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.439872370214957</v>
       </c>
       <c r="O15" t="n">
-        <v>-28.16159727442432</v>
+        <v>16.42792488608161</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>15.60550082657199</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>16.46798512610517</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2141,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.5819261365744327</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-1.475462685247075</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -2159,19 +2159,19 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-2.723285606951114</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.576222444784207</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>11.44831120197395</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>13.67190820985699</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>15.84842555965021</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.602246001538805</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>5.530407213910946</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2198,21 +2198,21 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>5.139031126558099</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>0.5454495722126946</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>5.049791993425586</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>18.74092126346848</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>38.39856510910838</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.124625794116042</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>10.15530698853429</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2239,19 +2239,19 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>23.69877968611682</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.301202142182699</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>15.60550082657199</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.95662139729773</v>
+        <v>25.36028734692464</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>51.91216676124913</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-1.475462685247074</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-6.912828115024684</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2278,19 +2278,19 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-13.76609940898933</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.508714021200267</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>24.12121622154257</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>38.5077583072274</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>55.30620345657083</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.031657194942603</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>7.76217934737705</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2317,21 +2317,21 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>6.456376566773256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>1.449521828263224</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>11.17828061640937</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>38.39856510910838</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>95.71472975852407</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.088945385966567</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>17.40650157142676</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2358,19 +2358,19 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>47.39092645945158</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.272781618054275</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>16.46798512610517</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>51.91216676124913</v>
       </c>
       <c r="Q17" t="n">
-        <v>-17.95662139729709</v>
+        <v>39.05462463097899</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-2.723285606951114</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-13.76609940898933</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2397,19 +2397,19 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-43.12718909070011</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.512122142873354</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>36.21567214747493</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>78.68980267650088</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>151.1499475879253</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.5487270400261994</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>3.978407090882079</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>11.56233920550879</v>
       </c>
     </row>
     <row r="18">
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.01064078252761629</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.3758371805596656</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.8333571581880166</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2492,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-9.507972103246219</v>
+        <v>1.192134315798659</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.766832501424194</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.382854560945209</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>0.7651230248262965</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.27280487236772</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.097514897426634</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.01064078252761629</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.3758371805596658</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2593,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8333571581880166</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-6.323852495613346</v>
+        <v>1.192134315798659</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2623,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.766832501424194</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.382854560945209</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.7651230248262962</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.272804872367719</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -2671,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.097514897426633</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
@@ -2679,16 +2679,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>-0.004917756917705785</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>-0.1787429074991289</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>-1.124625794116042</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-2.088945385966567</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.2169371577703999</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1.248713956425854</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2715,19 +2715,19 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0.9306538784753915</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.03612803534483141</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.5819261365744327</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.475462685247074</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.723285606951114</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-5.027470949428402</v>
+        <v>1.477838631755247</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.250101211246582</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.194957394976628</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>-0.6378678045689179</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>-2.760336696370763</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>-2.520531082126993</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>-2.802640033063934</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>-0.2074482860328148</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>0.8149003037378533</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.178655034612895</v>
       </c>
     </row>
     <row r="21">
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.3758371805596659</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4.550080082221125</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>12.8982716519249</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.766832501424194</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.77695853862113</v>
+        <v>-13.40329958962834</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>20.18728619194507</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2888,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>3.676068662738705</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>13.81389572988589</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>18.37925462552074</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.3758371805596659</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>4.550080082221125</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>12.8982716519249</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.766832501424194</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-4.776958538621041</v>
+        <v>-13.40329958962834</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>20.18728619194507</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>3.676068662738704</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>13.81389572988588</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>18.37925462552075</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
@@ -3036,16 +3036,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>-0.4570860794626933</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>-3.971360158404172</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>-10.15530698853429</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-17.40650157142676</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-1.248713956425855</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-5.357830832620333</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3072,19 +3072,19 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.3636216678918154</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>-0.03074431601516749</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-1.475462685247075</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-6.912828115024684</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-13.76609940898933</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.250101211246582</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5661697686769985</v>
+        <v>-7.381924980802701</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -3111,19 +3111,19 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>44.03641252598699</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>-1.586326549568464</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>-10.86627905110093</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>-15.44425040665211</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>-23.12502089407928</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>4.911791365184697</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3141,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>16.06636222813914</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>28.31024971547307</v>
       </c>
     </row>
     <row r="24">
@@ -3167,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.8333571581880173</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>12.8982716519249</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>68.09819569804129</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.382854560945209</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>20.18728619194507</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.566169768677408</v>
+        <v>-486.8332616027242</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>4.518849650494094</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>37.24777675403165</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>129.7348004269145</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.8333571581880168</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>12.89827165192491</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3307,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>68.09819569804129</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.382854560945209</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -3337,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>20.18728619194507</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.6650602861264325</v>
+        <v>-486.8332616027242</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>4.518849650494094</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>37.24777675403165</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>129.7348004269146</v>
       </c>
       <c r="AM25" t="n">
         <v>0</v>
@@ -3393,16 +3393,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>-1.16868944234641</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>-9.21881277318213</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>-23.69877968611681</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-47.39092645945157</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.930653878475391</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.3636216678918136</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -3429,19 +3429,19 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>23.68879886756204</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>-0.03310305217715067</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>-2.723285606951114</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-13.76609940898933</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-43.12718909070011</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3450,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.194957394976628</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>44.03641252598699</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -3468,19 +3468,19 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.9478815385520341</v>
+        <v>-436.8057222575121</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>-1.877188462822925</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>-17.2616970864677</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>-34.62715650309303</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>-60.6386162974352</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>8.709720073795213</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>42.56472805406715</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -3507,21 +3507,21 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>145.0244454550882</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>0.05955589180169553</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1.576222444784207</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>3.508714021200267</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>4.512122142873354</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.6378678045689179</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3539,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.586326549568464</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3548,19 +3548,19 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.877188462822925</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.05955589180169553</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.576222444784207</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.508714021200267</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.512122142873354</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>-0.6378678045689179</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>-1.586326549568464</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -3587,19 +3587,19 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>-1.877188462822925</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.284165238006862</v>
+        <v>7.31231103509213</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>9.566067929219599</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>5.02662268669918</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>5.060475449234733</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3631,16 +3631,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0</v>
+        <v>1.418553104775894</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>11.44831120197395</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>24.12121622154257</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>36.21567214747493</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2.760336696370763</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3658,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>10.86627905110093</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3667,19 +3667,19 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>17.2616970864677</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.418553104775894</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>11.44831120197395</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>24.12121622154257</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>36.21567214747493</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>-2.760336696370763</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>-10.86627905110093</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -3706,19 +3706,19 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>-17.2616970864677</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>9.566067929219599</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.284165238006926</v>
+        <v>33.85330624567014</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>36.22964287190445</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>41.72869520649253</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3750,16 +3750,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>1.831416724125386</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>13.67190820985699</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>38.5077583072274</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>78.68980267650088</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2.520531082126993</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>15.44425040665211</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3786,19 +3786,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>34.62715650309303</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.831416724125386</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>13.67190820985699</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>38.5077583072274</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>78.68980267650088</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>-2.520531082126993</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3816,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>-15.44425040665211</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -3825,19 +3825,19 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>-34.62715650309303</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>5.02662268669918</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>36.22964287190445</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.541161854938243</v>
+        <v>38.28138756538412</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>94.62701925298215</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3869,16 +3869,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>2.138875613550525</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>15.84842555965021</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>55.30620345657083</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>151.1499475879253</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.802640033063934</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>23.12502089407928</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3905,19 +3905,19 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>60.6386162974352</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.138875613550525</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>15.84842555965021</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>55.30620345657083</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>151.1499475879253</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>-2.802640033063934</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>-23.12502089407928</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -3944,19 +3944,19 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>-60.6386162974352</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>5.060475449234733</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>41.72869520649253</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>94.62701925298215</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.724611937281866</v>
+        <v>1.784547761482713</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.7651230248262965</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.676068662738705</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>4.518849650494094</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>0.7651230248262965</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -4048,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.676068662738705</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.518849650494094</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -4078,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>3.249959986581969</v>
+        <v>1.73621494614338</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>5.17361296662818</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>4.519611486538499</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -4122,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.7651230248262962</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3.676068662738704</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4140,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>4.518849650494094</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4161,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>0.7651230248262962</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>3.676068662738704</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>4.518849650494094</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>3.664462994468991</v>
+        <v>1.73621494614338</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>5.17361296662818</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>4.519611486538499</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
@@ -4226,16 +4226,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0</v>
+        <v>-0.5964506393073215</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>-3.602246001538805</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>-3.031657194942603</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-0.5487270400261994</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -4244,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.2074482860328148</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>4.911791365184697</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4262,19 +4262,19 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>8.709720073795213</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.5964506393073215</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.602246001538805</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.031657194942603</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>0.5487270400261994</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4283,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>-0.2074482860328148</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>4.911791365184697</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>8.709720073795213</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>11.16549252035082</v>
+        <v>5.38670493979505</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>10.35444592154595</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>10.81502174551066</v>
       </c>
     </row>
     <row r="34">
@@ -4357,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1.27280487236772</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -4366,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>13.81389572988589</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>37.24777675403165</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.27280487236772</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>13.81389572988589</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -4414,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>37.24777675403165</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -4435,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>5.17361296662818</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>11.27769499484176</v>
+        <v>-65.91517041382774</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>47.8711030872023</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1.272804872367719</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -4488,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>13.81389572988588</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4497,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>37.24777675403165</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.272804872367719</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>13.81389572988588</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>37.24777675403165</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>5.17361296662818</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>11.6579762866647</v>
+        <v>-65.91517041382774</v>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
@@ -4575,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>47.87110308720229</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
@@ -4583,16 +4583,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0</v>
+        <v>-0.773537103112676</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>-5.530407213910946</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>-7.76217934737705</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>-3.978407090882079</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.8149003037378533</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>16.06636222813914</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -4619,19 +4619,19 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>42.56472805406715</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>0.773537103112676</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>5.530407213910946</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>7.76217934737705</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.978407090882079</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4640,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>0.8149003037378533</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>16.06636222813914</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>42.56472805406715</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>10.35444592154595</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>11.65797628666481</v>
+        <v>-55.89272985088042</v>
       </c>
       <c r="AK36" t="n">
         <v>0</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>63.78466195801781</v>
       </c>
     </row>
     <row r="37">
@@ -4714,7 +4714,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1.097514897426634</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -4723,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>18.37925462552074</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -4732,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>129.7348004269145</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.097514897426634</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -4762,7 +4762,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>18.37925462552074</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4771,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>129.7348004269145</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -4792,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>4.519611486538499</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -4801,7 +4801,7 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>47.8711030872023</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>27.34326986756605</v>
+        <v>-2793.434313004652</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1.097514897426633</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>18.37925462552075</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4854,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>129.7348004269146</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4875,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.097514897426633</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>18.37925462552075</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>129.7348004269146</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>4.519611486538499</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>47.87110308720229</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>40.05967303184045</v>
+        <v>-2793.434313004652</v>
       </c>
       <c r="AM38" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0</v>
+        <v>-0.8272631971284673</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>-5.139031126558099</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>-6.456376566773256</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>-11.56233920550879</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1.178655034612895</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -4967,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>28.31024971547307</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -4976,19 +4976,19 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>145.0244454550882</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>0.8272631971284673</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>5.139031126558099</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>6.456376566773256</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>11.56233920550879</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4997,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.178655034612895</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>28.31024971547307</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5015,7 +5015,7 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>145.0244454550882</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>10.81502174551066</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>63.78466195801781</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
@@ -5054,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>459.1634949960236</v>
+        <v>-2754.828586295333</v>
       </c>
     </row>
   </sheetData>

--- a/hamiltonian_core_matrix.xlsx
+++ b/hamiltonian_core_matrix.xlsx
@@ -418,13 +418,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>21.87244733340265</v>
+        <v>-36.50293397851359</v>
       </c>
       <c r="B1" t="n">
-        <v>-8.175308300775619</v>
+        <v>-8.175308303198394</v>
       </c>
       <c r="C1" t="n">
-        <v>-5.950228597926256</v>
+        <v>-5.950228597717681</v>
       </c>
       <c r="D1" t="n">
         <v>0</v>
@@ -433,7 +433,7 @@
         <v>0</v>
       </c>
       <c r="F1" t="n">
-        <v>-0.1210478808899644</v>
+        <v>-0.121047880893802</v>
       </c>
       <c r="G1" t="n">
         <v>0</v>
@@ -442,16 +442,16 @@
         <v>0</v>
       </c>
       <c r="I1" t="n">
-        <v>-0.01668018157227426</v>
+        <v>-0.01668018157168956</v>
       </c>
       <c r="J1" t="n">
-        <v>-2.7569229055326e-23</v>
+        <v>-2.756922905339322e-23</v>
       </c>
       <c r="K1" t="n">
-        <v>-8.193231505337367e-07</v>
+        <v>-8.072138206607453e-07</v>
       </c>
       <c r="L1" t="n">
-        <v>-0.04117906320328268</v>
+        <v>-0.03971932119720709</v>
       </c>
       <c r="M1" t="n">
         <v>0</v>
@@ -460,7 +460,7 @@
         <v>0</v>
       </c>
       <c r="O1" t="n">
-        <v>4.092822285924705e-06</v>
+        <v>3.852309536740238e-06</v>
       </c>
       <c r="P1" t="n">
         <v>0</v>
@@ -469,16 +469,16 @@
         <v>0</v>
       </c>
       <c r="R1" t="n">
-        <v>0.1761813352111002</v>
+        <v>0.174609884293132</v>
       </c>
       <c r="S1" t="n">
-        <v>-0.0003593238765716624</v>
+        <v>-0.0003588592883688263</v>
       </c>
       <c r="T1" t="n">
-        <v>-0.9857516988835008</v>
+        <v>-0.9509434351773246</v>
       </c>
       <c r="U1" t="n">
-        <v>-1.937154335997275</v>
+        <v>-1.929869412404118</v>
       </c>
       <c r="V1" t="n">
         <v>0</v>
@@ -487,7 +487,7 @@
         <v>0</v>
       </c>
       <c r="X1" t="n">
-        <v>1.916567027581616</v>
+        <v>1.896198682728335</v>
       </c>
       <c r="Y1" t="n">
         <v>0</v>
@@ -496,18 +496,18 @@
         <v>0</v>
       </c>
       <c r="AA1" t="n">
-        <v>3.398647472836053</v>
+        <v>3.398185100225847</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-8.175308300775619</v>
+        <v>-8.175308303198394</v>
       </c>
       <c r="B2" t="n">
-        <v>-14.53042300426348</v>
+        <v>-13.38180739049832</v>
       </c>
       <c r="C2" t="n">
-        <v>-10.0336321360312</v>
+        <v>-10.03262107472495</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -516,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8258932807273313</v>
+        <v>-0.825782665766823</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -525,16 +525,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.547886632726138</v>
+        <v>-0.5452322485065547</v>
       </c>
       <c r="J2" t="n">
-        <v>-8.193231505337366e-07</v>
+        <v>-8.072138206607452e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.001896857497600757</v>
+        <v>-0.001896857244586663</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.217974233717204</v>
+        <v>-0.1994420297707155</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005179769966008722</v>
+        <v>0.005179435278039555</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.933754470875666</v>
+        <v>0.6924569130542471</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.316085493350853</v>
+        <v>-0.294544205767221</v>
       </c>
       <c r="T2" t="n">
-        <v>-3.244581350973903</v>
+        <v>-2.859645468048795</v>
       </c>
       <c r="U2" t="n">
-        <v>-4.280133396185333</v>
+        <v>-4.159630142637329</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>5.591269421279414</v>
+        <v>4.369593829736191</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -579,18 +579,18 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.284043095196727</v>
+        <v>6.184097202662103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-5.950228597926256</v>
+        <v>-5.950228597717681</v>
       </c>
       <c r="B3" t="n">
-        <v>-10.0336321360312</v>
+        <v>-10.03262107472495</v>
       </c>
       <c r="C3" t="n">
-        <v>-11.51041456401506</v>
+        <v>-10.72822515971567</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -599,7 +599,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8034310771642938</v>
+        <v>-0.8001235669443573</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -608,16 +608,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.601989910290022</v>
+        <v>-1.411604336325851</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.04117906320328268</v>
+        <v>-0.03971932119720708</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.217974233717204</v>
+        <v>-0.1994420297707155</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9383983422588892</v>
+        <v>-0.9260178193059923</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3186078137952448</v>
+        <v>0.2628811117764718</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -635,16 +635,16 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.26029682781021</v>
+        <v>2.063643705842018</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.853903498876998</v>
+        <v>-1.828759444568596</v>
       </c>
       <c r="T3" t="n">
-        <v>-5.508162634814227</v>
+        <v>-5.037246673350118</v>
       </c>
       <c r="U3" t="n">
-        <v>-7.271229513450862</v>
+        <v>-6.404700671084194</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5.222537808063837</v>
+        <v>4.401148103631909</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.172024489455182</v>
+        <v>6.678025803821707</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-8.395604860786429</v>
+        <v>-11.83115720932403</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.432964435868629</v>
+        <v>-5.399567427233988</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0006455902676876036</v>
+        <v>-0.0006451762465812252</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -712,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.140136563055478</v>
+        <v>-0.0974762240810232</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.483972903460318</v>
+        <v>-1.313066829369554</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.917681396209502</v>
+        <v>-1.861552876928129</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.395604860786429</v>
+        <v>-11.83115720932403</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.432964435868629</v>
+        <v>-5.399567427233988</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0006455902676876036</v>
+        <v>-0.0006451762465812252</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.140136563055478</v>
+        <v>-0.0974762240810232</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.483972903460318</v>
+        <v>-1.313066829369554</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1.917681396209502</v>
+        <v>-1.861552876928129</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -833,13 +833,13 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.1210478808899644</v>
+        <v>-0.121047880893802</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.8258932807273313</v>
+        <v>-0.825782665766823</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.8034310771642938</v>
+        <v>-0.8001235669443573</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.740677669290836</v>
+        <v>-12.1758823483431</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -857,16 +857,16 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.787988901981586</v>
+        <v>-5.745754821385668</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.092822285924705e-06</v>
+        <v>-3.852309536740238e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.005179769966008722</v>
+        <v>-0.005179435278039555</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3186078137952448</v>
+        <v>-0.2628811117764718</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01348516578008441</v>
+        <v>0.01347627337328851</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -884,16 +884,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.268908634434464</v>
+        <v>0.8125443388068054</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7884815630233999</v>
+        <v>-0.6687824592917403</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.426662160522219</v>
+        <v>-3.093703249759801</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.159456991619736</v>
+        <v>-2.154885116612308</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>4.497944494640891</v>
+        <v>3.97740047978849</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.279217089357184</v>
+        <v>1.220476164101141</v>
       </c>
     </row>
     <row r="7">
@@ -925,7 +925,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.432964435868629</v>
+        <v>-5.399567427233988</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-10.53561227900119</v>
+        <v>-7.715283860180842</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.140136563055478</v>
+        <v>-0.0974762240810232</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8666470110314599</v>
+        <v>-0.6936900232863972</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-4.011483349174307</v>
+        <v>-3.122749492998057</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-4.639847988123597</v>
+        <v>-4.521722662776479</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.432964435868629</v>
+        <v>-5.399567427233988</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-10.53561227900119</v>
+        <v>-7.715283860180842</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.140136563055478</v>
+        <v>-0.0974762240810232</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.8666470110314598</v>
+        <v>-0.6936900232863971</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-4.011483349174307</v>
+        <v>-3.122749492998057</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>-4.639847988123597</v>
+        <v>-4.521722662776479</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.01668018157227426</v>
+        <v>-0.01668018157168956</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.547886632726138</v>
+        <v>-0.5452322485065547</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.601989910290022</v>
+        <v>-1.411604336325851</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.787988901981586</v>
+        <v>-5.745754821385668</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1106,16 +1106,16 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-12.38154427960635</v>
+        <v>-8.938903477036988</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1761813352111002</v>
+        <v>-0.174609884293132</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9337544708756662</v>
+        <v>-0.6924569130542472</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.26029682781021</v>
+        <v>-2.063643705842018</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.268908634434464</v>
+        <v>0.8125443388068054</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4.526786856597904</v>
+        <v>3.711744522568024</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.930570167669011</v>
+        <v>-3.923172166807364</v>
       </c>
       <c r="T9" t="n">
-        <v>-8.41822381292471</v>
+        <v>-7.17244585129201</v>
       </c>
       <c r="U9" t="n">
-        <v>-6.715883343090409</v>
+        <v>-5.866796646101558</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.611681378798007</v>
+        <v>2.842037740087108</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1160,18 +1160,18 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2448201044171232</v>
+        <v>0.4757246044603474</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-2.7569229055326e-23</v>
+        <v>-2.756922905339322e-23</v>
       </c>
       <c r="B10" t="n">
-        <v>-8.193231505337366e-07</v>
+        <v>-8.072138206607452e-07</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.04117906320328268</v>
+        <v>-0.03971932119720708</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.092822285924705e-06</v>
+        <v>-3.852309536740238e-06</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1189,16 +1189,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1761813352111002</v>
+        <v>-0.174609884293132</v>
       </c>
       <c r="J10" t="n">
-        <v>21.87244733340265</v>
+        <v>-36.50293397851359</v>
       </c>
       <c r="K10" t="n">
-        <v>-8.175308300775619</v>
+        <v>-8.175308303198394</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.950228597926256</v>
+        <v>-5.950228597717681</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1210478808899644</v>
+        <v>0.121047880893802</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1216,16 +1216,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01668018157227426</v>
+        <v>0.01668018157168956</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0003593238765716624</v>
+        <v>-0.0003588592883688263</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9857516988835008</v>
+        <v>-0.9509434351773246</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.937154335997275</v>
+        <v>-1.929869412404118</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.916567027581616</v>
+        <v>-1.896198682728335</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1243,18 +1243,18 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-3.398647472836053</v>
+        <v>-3.398185100225847</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-8.193231505337367e-07</v>
+        <v>-8.072138206607453e-07</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.001896857497600757</v>
+        <v>-0.001896857244586663</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.217974233717204</v>
+        <v>-0.1994420297707155</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.005179769966008722</v>
+        <v>-0.005179435278039555</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1272,16 +1272,16 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9337544708756662</v>
+        <v>-0.6924569130542472</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.175308300775619</v>
+        <v>-8.175308303198394</v>
       </c>
       <c r="K11" t="n">
-        <v>-14.53042300426348</v>
+        <v>-13.38180739049832</v>
       </c>
       <c r="L11" t="n">
-        <v>-10.0336321360312</v>
+        <v>-10.03262107472495</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8258932807273313</v>
+        <v>0.825782665766823</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.547886632726138</v>
+        <v>0.5452322485065547</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.316085493350853</v>
+        <v>-0.294544205767221</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.244581350973903</v>
+        <v>-2.859645468048795</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.280133396185333</v>
+        <v>-4.159630142637329</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.591269421279414</v>
+        <v>-4.369593829736191</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1326,18 +1326,18 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-6.284043095196727</v>
+        <v>-6.184097202662103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.04117906320328268</v>
+        <v>-0.03971932119720709</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.217974233717204</v>
+        <v>-0.1994420297707155</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.9383983422588892</v>
+        <v>-0.9260178193059923</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3186078137952448</v>
+        <v>-0.2628811117764718</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1355,16 +1355,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.26029682781021</v>
+        <v>-2.063643705842018</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.950228597926256</v>
+        <v>-5.950228597717681</v>
       </c>
       <c r="K12" t="n">
-        <v>-10.0336321360312</v>
+        <v>-10.03262107472495</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.51041456401506</v>
+        <v>-10.72822515971567</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8034310771642938</v>
+        <v>0.8001235669443573</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1382,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.601989910290022</v>
+        <v>1.411604336325851</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.853903498876998</v>
+        <v>-1.828759444568596</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.508162634814227</v>
+        <v>-5.037246673350118</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.271229513450862</v>
+        <v>-6.404700671084194</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.222537808063837</v>
+        <v>-4.401148103631909</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-7.172024489455182</v>
+        <v>-6.678025803821707</v>
       </c>
     </row>
     <row r="13">
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0006455902676876036</v>
+        <v>-0.0006451762465812252</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.140136563055478</v>
+        <v>-0.0974762240810232</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.395604860786429</v>
+        <v>-11.83115720932403</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.432964435868629</v>
+        <v>-5.399567427233988</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.483972903460318</v>
+        <v>-1.313066829369554</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.917681396209502</v>
+        <v>-1.861552876928129</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0006455902676876036</v>
+        <v>-0.0006451762465812252</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.140136563055478</v>
+        <v>-0.0974762240810232</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.395604860786429</v>
+        <v>-11.83115720932403</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.432964435868629</v>
+        <v>-5.399567427233988</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-1.483972903460318</v>
+        <v>-1.313066829369554</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>-1.917681396209502</v>
+        <v>-1.861552876928129</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -1580,13 +1580,13 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4.092822285924705e-06</v>
+        <v>3.852309536740238e-06</v>
       </c>
       <c r="B15" t="n">
-        <v>0.005179769966008722</v>
+        <v>0.005179435278039555</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3186078137952448</v>
+        <v>0.2628811117764718</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01348516578008441</v>
+        <v>0.01347627337328851</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1604,16 +1604,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1.268908634434464</v>
+        <v>0.8125443388068054</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1210478808899644</v>
+        <v>0.121047880893802</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8258932807273313</v>
+        <v>0.825782665766823</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8034310771642938</v>
+        <v>0.8001235669443573</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.740677669290836</v>
+        <v>-12.1758823483431</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1631,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-5.787988901981586</v>
+        <v>-5.745754821385668</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7884815630233999</v>
+        <v>0.6687824592917403</v>
       </c>
       <c r="T15" t="n">
-        <v>3.426662160522219</v>
+        <v>3.093703249759801</v>
       </c>
       <c r="U15" t="n">
-        <v>2.159456991619736</v>
+        <v>2.154885116612308</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.497944494640891</v>
+        <v>3.97740047978849</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.279217089357184</v>
+        <v>1.220476164101141</v>
       </c>
     </row>
     <row r="16">
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.140136563055478</v>
+        <v>-0.0974762240810232</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1681,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8666470110314599</v>
+        <v>-0.6936900232863972</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.432964435868629</v>
+        <v>-5.399567427233988</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-10.53561227900119</v>
+        <v>-7.715283860180842</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.011483349174307</v>
+        <v>-3.122749492998057</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>-4.639847988123597</v>
+        <v>-4.521722662776479</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.140136563055478</v>
+        <v>-0.0974762240810232</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8666470110314598</v>
+        <v>-0.6936900232863971</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.432964435868629</v>
+        <v>-5.399567427233988</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-10.53561227900119</v>
+        <v>-7.715283860180842</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-4.011483349174307</v>
+        <v>-3.122749492998057</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>-4.639847988123597</v>
+        <v>-4.521722662776479</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -1829,13 +1829,13 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1761813352111002</v>
+        <v>0.174609884293132</v>
       </c>
       <c r="B18" t="n">
-        <v>0.933754470875666</v>
+        <v>0.6924569130542471</v>
       </c>
       <c r="C18" t="n">
-        <v>2.26029682781021</v>
+        <v>2.063643705842018</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.268908634434464</v>
+        <v>0.8125443388068054</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1853,16 +1853,16 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4.526786856597904</v>
+        <v>3.711744522568024</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01668018157227426</v>
+        <v>0.01668018157168956</v>
       </c>
       <c r="K18" t="n">
-        <v>0.547886632726138</v>
+        <v>0.5452322485065547</v>
       </c>
       <c r="L18" t="n">
-        <v>1.601989910290022</v>
+        <v>1.411604336325851</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-5.787988901981586</v>
+        <v>-5.745754821385668</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1880,16 +1880,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-12.38154427960635</v>
+        <v>-8.938903477036988</v>
       </c>
       <c r="S18" t="n">
-        <v>3.930570167669011</v>
+        <v>3.923172166807364</v>
       </c>
       <c r="T18" t="n">
-        <v>8.41822381292471</v>
+        <v>7.17244585129201</v>
       </c>
       <c r="U18" t="n">
-        <v>6.715883343090409</v>
+        <v>5.866796646101558</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.611681378798007</v>
+        <v>2.842037740087108</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -1907,18 +1907,18 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.2448201044171232</v>
+        <v>0.4757246044603474</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.0003593238765716624</v>
+        <v>-0.0003588592883688263</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.316085493350853</v>
+        <v>-0.294544205767221</v>
       </c>
       <c r="C19" t="n">
-        <v>-1.853903498876998</v>
+        <v>-1.828759444568596</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7884815630233999</v>
+        <v>-0.6687824592917403</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1936,16 +1936,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.930570167669011</v>
+        <v>-3.923172166807364</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0003593238765716624</v>
+        <v>-0.0003588592883688263</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.316085493350853</v>
+        <v>-0.294544205767221</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.853903498876998</v>
+        <v>-1.828759444568596</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7884815630233999</v>
+        <v>0.6687824592917403</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1963,16 +1963,16 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.930570167669011</v>
+        <v>3.923172166807364</v>
       </c>
       <c r="S19" t="n">
-        <v>6.32683306482992</v>
+        <v>-25.24417399172263</v>
       </c>
       <c r="T19" t="n">
-        <v>-5.25934687968538</v>
+        <v>-5.259346879323102</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.507855846539031</v>
+        <v>-4.507855846904524</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1995,13 +1995,13 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.9857516988835008</v>
+        <v>-0.9509434351773246</v>
       </c>
       <c r="B20" t="n">
-        <v>-3.244581350973903</v>
+        <v>-2.859645468048795</v>
       </c>
       <c r="C20" t="n">
-        <v>-5.508162634814227</v>
+        <v>-5.037246673350118</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.426662160522219</v>
+        <v>-3.093703249759801</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2019,16 +2019,16 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-8.41822381292471</v>
+        <v>-7.17244585129201</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9857516988835008</v>
+        <v>-0.9509434351773246</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.244581350973903</v>
+        <v>-2.859645468048795</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.508162634814227</v>
+        <v>-5.037246673350118</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.426662160522219</v>
+        <v>3.093703249759801</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2046,16 +2046,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>8.41822381292471</v>
+        <v>7.17244585129201</v>
       </c>
       <c r="S20" t="n">
-        <v>-5.25934687968538</v>
+        <v>-5.259346879323102</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.17845109350725</v>
+        <v>-12.0765739123006</v>
       </c>
       <c r="U20" t="n">
-        <v>-9.757948481291674</v>
+        <v>-9.700034868813017</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2078,13 +2078,13 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1.937154335997275</v>
+        <v>-1.929869412404118</v>
       </c>
       <c r="B21" t="n">
-        <v>-4.280133396185333</v>
+        <v>-4.159630142637329</v>
       </c>
       <c r="C21" t="n">
-        <v>-7.271229513450862</v>
+        <v>-6.404700671084194</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.159456991619736</v>
+        <v>-2.154885116612308</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2102,16 +2102,16 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-6.715883343090409</v>
+        <v>-5.866796646101558</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.937154335997275</v>
+        <v>-1.929869412404118</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.280133396185333</v>
+        <v>-4.159630142637329</v>
       </c>
       <c r="L21" t="n">
-        <v>-7.271229513450862</v>
+        <v>-6.404700671084194</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.159456991619736</v>
+        <v>2.154885116612308</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2129,16 +2129,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.715883343090409</v>
+        <v>5.866796646101558</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.507855846539031</v>
+        <v>-4.507855846904524</v>
       </c>
       <c r="T21" t="n">
-        <v>-9.757948481291674</v>
+        <v>-9.700034868813017</v>
       </c>
       <c r="U21" t="n">
-        <v>-11.85061346586761</v>
+        <v>-10.45508412352509</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.483972903460318</v>
+        <v>-1.313066829369554</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.011483349174307</v>
+        <v>-3.122749492998057</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.483972903460318</v>
+        <v>-1.313066829369554</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.011483349174307</v>
+        <v>-3.122749492998057</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-10.78608858266407</v>
+        <v>-10.86218058679919</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>-6.339755451134696</v>
+        <v>-5.622291299772129</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.483972903460318</v>
+        <v>-1.313066829369554</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.011483349174307</v>
+        <v>-3.122749492998057</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.483972903460318</v>
+        <v>-1.313066829369554</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.011483349174307</v>
+        <v>-3.122749492998057</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-10.78608858266407</v>
+        <v>-10.86218058679919</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>-6.339755451134696</v>
+        <v>-5.622291299772129</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -2327,13 +2327,13 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1.916567027581616</v>
+        <v>1.896198682728335</v>
       </c>
       <c r="B24" t="n">
-        <v>5.591269421279414</v>
+        <v>4.369593829736191</v>
       </c>
       <c r="C24" t="n">
-        <v>5.222537808063837</v>
+        <v>4.401148103631909</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4.497944494640891</v>
+        <v>3.97740047978849</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2351,16 +2351,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3.611681378798007</v>
+        <v>2.842037740087108</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.916567027581616</v>
+        <v>-1.896198682728335</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.591269421279414</v>
+        <v>-4.369593829736191</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.222537808063837</v>
+        <v>-4.401148103631909</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.497944494640891</v>
+        <v>3.97740047978849</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.611681378798007</v>
+        <v>2.842037740087108</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-12.29876270547611</v>
+        <v>-12.30150733454652</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2405,7 +2405,7 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>-8.003987693426037</v>
+        <v>-6.918958619276077</v>
       </c>
     </row>
     <row r="25">
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.917681396209502</v>
+        <v>-1.861552876928129</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.639847988123597</v>
+        <v>-4.521722662776479</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.917681396209502</v>
+        <v>-1.861552876928129</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.639847988123597</v>
+        <v>-4.521722662776479</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.339755451134696</v>
+        <v>-5.622291299772129</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -2482,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>-13.11028021019357</v>
+        <v>-7.525207159747448</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -2505,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.917681396209502</v>
+        <v>-1.861552876928129</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.639847988123597</v>
+        <v>-4.521722662776479</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.917681396209502</v>
+        <v>-1.861552876928129</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.639847988123597</v>
+        <v>-4.521722662776479</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-6.339755451134696</v>
+        <v>-5.622291299772129</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>-13.11028021019357</v>
+        <v>-7.525207159747448</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -2576,13 +2576,13 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3.398647472836053</v>
+        <v>3.398185100225847</v>
       </c>
       <c r="B27" t="n">
-        <v>6.284043095196727</v>
+        <v>6.184097202662103</v>
       </c>
       <c r="C27" t="n">
-        <v>7.172024489455182</v>
+        <v>6.678025803821707</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.279217089357184</v>
+        <v>1.220476164101141</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2600,16 +2600,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2448201044171232</v>
+        <v>0.4757246044603474</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.398647472836053</v>
+        <v>-3.398185100225847</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.284043095196727</v>
+        <v>-6.184097202662103</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.172024489455182</v>
+        <v>-6.678025803821707</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.279217089357184</v>
+        <v>1.220476164101141</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2448201044171232</v>
+        <v>0.4757246044603474</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.003987693426037</v>
+        <v>-6.918958619276077</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>-19.91205434704512</v>
+        <v>-9.803447848525751</v>
       </c>
     </row>
   </sheetData>
